--- a/internal_doc/05.测试设计/story/FullTextSearch/全文检索查询.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/全文检索查询.xlsx
@@ -16,13 +16,161 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
-  <si>
-    <t>结构化搜索</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全文搜索</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+  <si>
+    <t>common terms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结合cutoff_frequency、minimum_should_match</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上并结合fields、type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构化搜索(精确查询)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文搜索(模糊查询)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 分词查询，查询会按照先分词后匹配的顺序；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>match_prase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>match_prase_prefix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结合operator、minimum_should_match</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multi_match</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合must、must_not、should</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dis_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结合tie_break、boost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simple query string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配合正则表达式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 完全匹配，文档必须匹配完整词汇；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. term 的复数形式，可通过数组指定搜索多个完整词汇；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 短语前缀匹配，与match_phrase查询相似；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 多字段匹配，相当于多个不同字段、相同查询的match；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作用与query string相似</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如：{'query': {'bool': {'must': {'match': { match1 }, 'should': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'match': { match2 }},{'match': { match3 }}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -30,6 +178,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>terms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 范围查询，主要用在搜索数值、日期范围；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>多词查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -38,75 +198,615 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>match_prase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>common terms</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结合cutoff_frequency、minimum_should_match</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>multi_match</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>match_prase_prefix</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合must、must_not、should</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>simple query string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配合正则表达式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>terms</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dis_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结合operator、minimum_should_match</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上并结合fields、type</t>
+    <t>2. 如查询'a b c'，先拆成'a'、b'、'c'，再匹配其中任意一个词汇；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 查询结果按照评分排序，如同时包含'a'、'b'、'c'，则该记录最高分，位于第一条；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 短语匹配，返回记录必须匹配短语的分词，且各分词的相对位置不变；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 短语中最后一个词汇作为前缀，如查'Hello Wo'后任意记录：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{'query': {'match_phrase_prefix': {'field': 'Hello Wo'}}} </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 如查询字段field1、field2都包含'Hello World'：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>operator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 操作符，如and、or；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minimum_should_match</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>： 至少需要匹配的词汇数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：字段；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>must</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 文档必须完全匹配条件；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>should</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 相当于or，文档至少匹配一个条件；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>must_not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: must的取反，文档必须不匹配条件</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如：{'query': {'dis_max': {'queries': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'match' : { match1 }}, {'match' : { match2 }}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tie_break</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 改变查询子句的分值；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>boost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>： 改变查询子句的权重</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 重要词汇匹配，用于控制高频词和低频词；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cutoff_frequency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 将查询条件划分为低频组、高频组，可设置为分数/正整数；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minimum_should_match</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: 适用于低频词，表示至少匹配的词汇个数 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">查询支持通配符，如 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'query': {'query_string': {'query': '*ab?', 'fields': ['field']}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">{'multi_match': {'query': {'fields': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'field1', 'field2'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2. 如查询‘Hello World’：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'query': 'term': {'field': 'Hello World'}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. 如查询‘a’与‘b'： </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'query': {'terms': {'field':</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'a', 'b'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. 如查询1~10： </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'query': {'range': {'field': {'gte': 1,'lte': 10}}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 如查询包含短语'Hello World':</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{'query': {'match_phrase': {'field': Hello World'}}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>： 字段类型，有best_filelds、most_fields、cross_fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +814,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +855,56 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -176,11 +926,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,125 +1230,279 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.875" customWidth="1"/>
     <col min="2" max="2" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.5">
+    <row r="1" spans="1:7" ht="22.5">
       <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75">
+      <c r="F3" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20.25">
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75">
+      <c r="F6" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20.25">
+      <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75">
+      <c r="F9" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="22.5">
+      <c r="A12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75">
+      <c r="A13" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20.25">
+      <c r="A14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75">
+      <c r="F15" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75">
+      <c r="F16" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75">
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.75">
+      <c r="F18" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18.75">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18.75">
+      <c r="F21" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18.75">
+      <c r="F22" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18.75">
+      <c r="A24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="18.75">
+      <c r="F25" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.25">
+      <c r="F26" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18.75">
+      <c r="A28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="18.75">
+      <c r="F29" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="14.25">
+      <c r="F30" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18.75">
+      <c r="F31" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18.75">
+      <c r="F32" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="14.25">
+      <c r="A34" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="18.75">
+      <c r="A35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="18.75">
+      <c r="F36" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="18.75">
+      <c r="F37" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="14.25">
+      <c r="F38" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="18.75">
+      <c r="A40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="18.75">
+      <c r="F41" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.25">
+      <c r="F42" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:6" ht="14.25">
+      <c r="A44" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="18.75">
+      <c r="A45" s="6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="22.5">
-      <c r="A6" s="3" t="s">
+      <c r="B45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="14.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="F45" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="18.75">
+      <c r="A46" s="2"/>
+      <c r="F46" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18.75">
+      <c r="A47" s="2"/>
+      <c r="F47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="18.75">
+      <c r="A49" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="14.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:2" ht="14.25">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="F49" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="18.75">
+      <c r="A51" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.25">
-      <c r="A17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-    </row>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
